--- a/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/Score-A4.xlsx
@@ -1834,358 +1834,358 @@
       <left/>
       <right/>
       <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2193,8 +2193,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2202,8 +2202,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2211,50 +2211,50 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2262,8 +2262,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2271,8 +2271,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2280,8 +2280,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2289,8 +2289,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2298,8 +2298,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2307,8 +2307,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2316,8 +2316,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2325,8 +2325,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2334,134 +2334,134 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -2952,16 +2952,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="70" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="71" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="72" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3111,16 +3111,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="114" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="115" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="116" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="124" fillId="0" borderId="117" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3160,8 +3160,8 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyProtection="1" applyAlignment="1">
-      <protection locked="0"/>
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -3174,8 +3174,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1" applyAlignment="1" applyBorder="0">
-      <protection locked="0"/>
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0" applyFont="1">
       <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -4663,21 +4663,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C8:D8">
-    <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:F13">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns1:uid="{00000000-0002-0000-0000-000001000000}"/>
@@ -4690,7 +4675,6 @@
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="71" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
